--- a/Mantenimiento/excels/CALLAO-CALLAO-CALLAO.xlsx
+++ b/Mantenimiento/excels/CALLAO-CALLAO-CALLAO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1004,11 +954,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1056,11 +1001,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1108,11 +1048,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1160,11 +1095,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1212,11 +1142,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1264,11 +1189,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1316,11 +1236,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1368,11 +1283,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1420,11 +1330,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1472,11 +1377,6 @@
       <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1524,11 +1424,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1576,11 +1471,6 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1627,11 +1517,6 @@
       </c>
       <c r="K23" t="n">
         <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/Mantenimiento/excels/CALLAO-CALLAO-CALLAO.xlsx
+++ b/Mantenimiento/excels/CALLAO-CALLAO-CALLAO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,57 +417,57 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
@@ -516,20 +504,30 @@
           <t>76 MI AMIGO JESUS</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-12.04083</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-77.12267</v>
-      </c>
-      <c r="I2" t="n">
-        <v>331</v>
-      </c>
-      <c r="J2" t="n">
-        <v>13</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-12.04083</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-77.12267</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -563,20 +561,30 @@
           <t>94 MIGUEL GRAU</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-12.04614</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-77.10393000000001</v>
-      </c>
-      <c r="I3" t="n">
-        <v>294</v>
-      </c>
-      <c r="J3" t="n">
-        <v>13</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-12.04614</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-77.10393</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -610,20 +618,30 @@
           <t>5023 ABELARDO GAMARRA</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-12.05689</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-77.12657</v>
-      </c>
-      <c r="I4" t="n">
-        <v>568</v>
-      </c>
-      <c r="J4" t="n">
-        <v>25</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-12.05689</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-77.12657</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -657,20 +675,30 @@
           <t>4007 VIRGEN DEL PILAR</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-12.0549</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-77.11255</v>
-      </c>
-      <c r="I5" t="n">
-        <v>480</v>
-      </c>
-      <c r="J5" t="n">
-        <v>23</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-12.0549</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-77.11255</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -704,20 +732,30 @@
           <t>5031 CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-12.04287</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-77.10235</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1086</v>
-      </c>
-      <c r="J6" t="n">
-        <v>49</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-12.04287</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-77.10235</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -751,20 +789,30 @@
           <t>4018 ABRAHAM VALDELOMAR</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-12.04283</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-77.11144</v>
-      </c>
-      <c r="I7" t="n">
-        <v>765</v>
-      </c>
-      <c r="J7" t="n">
-        <v>40</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-12.04283</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-77.11144</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -798,20 +846,30 @@
           <t>5049 EMMA DETTMANN DE GUTIERREZ</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-12.05066</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-77.09526</v>
-      </c>
-      <c r="I8" t="n">
-        <v>781</v>
-      </c>
-      <c r="J8" t="n">
-        <v>45</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-12.05066</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-77.09526</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>781</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -845,20 +903,30 @@
           <t>5010 VIRGEN DE GUADALUPE</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-12.04644</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-77.10265</v>
-      </c>
-      <c r="I9" t="n">
-        <v>392</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-12.04644</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-77.10265</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -892,20 +960,30 @@
           <t>5076 NUESTRA SEÑORA DE LAS MERCEDES</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-11.9433</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-77.1326</v>
-      </c>
-      <c r="I10" t="n">
-        <v>2339</v>
-      </c>
-      <c r="J10" t="n">
-        <v>112</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-11.9433</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-77.1326</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2339</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -939,20 +1017,30 @@
           <t>5089 VIRGEN MARIA</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-11.99932</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-77.10861</v>
-      </c>
-      <c r="I11" t="n">
-        <v>722</v>
-      </c>
-      <c r="J11" t="n">
-        <v>27</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-11.99932</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-77.10861</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -986,20 +1074,30 @@
           <t>POLITECNICO NACIONAL DEL CALLAO</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-12.044294</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-77.099361</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1587</v>
-      </c>
-      <c r="J12" t="n">
-        <v>87</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-12.044294</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-77.099361</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1587</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -1033,20 +1131,30 @@
           <t>SANTA CRUZ</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-12.03214</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-77.09748</v>
-      </c>
-      <c r="I13" t="n">
-        <v>1051</v>
-      </c>
-      <c r="J13" t="n">
-        <v>59</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-12.03214</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-77.09748</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -1080,20 +1188,30 @@
           <t>LOS OLIVOS</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-12.02196</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-77.09209</v>
-      </c>
-      <c r="I14" t="n">
-        <v>347</v>
-      </c>
-      <c r="J14" t="n">
-        <v>28</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-12.02196</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-77.09209</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>347</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -1127,20 +1245,30 @@
           <t>FLORENCE NIGHTINGALE</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-12.01716</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-77.09765</v>
-      </c>
-      <c r="I15" t="n">
-        <v>327</v>
-      </c>
-      <c r="J15" t="n">
-        <v>21</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-12.01716</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-77.09765</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1174,20 +1302,30 @@
           <t>SAN JOSE HERMANOS MARISTAS</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-12.05654</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-77.12863</v>
-      </c>
-      <c r="I16" t="n">
-        <v>852</v>
-      </c>
-      <c r="J16" t="n">
-        <v>56</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-12.05654</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-77.12863</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -1221,20 +1359,30 @@
           <t>SAN LUIS GONZAGA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-12.01823</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-77.09402</v>
-      </c>
-      <c r="I17" t="n">
-        <v>436</v>
-      </c>
-      <c r="J17" t="n">
-        <v>20</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-12.01823</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-77.09402</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>436</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -1268,20 +1416,30 @@
           <t>MARIA REINA DE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-12.0022</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-77.10862</v>
-      </c>
-      <c r="I18" t="n">
-        <v>559</v>
-      </c>
-      <c r="J18" t="n">
-        <v>27</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-12.0022</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-77.10862</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>559</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -1315,20 +1473,30 @@
           <t>2093 SANTA ROSA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-11.989659</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-77.117276</v>
-      </c>
-      <c r="I19" t="n">
-        <v>600</v>
-      </c>
-      <c r="J19" t="n">
-        <v>30</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-11.989659</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-77.117276</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>600</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -1362,20 +1530,30 @@
           <t>MI DIVINO NIÑO JESUS GUADALUPANO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-12.04296</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-77.11915</v>
-      </c>
-      <c r="I20" t="n">
-        <v>86</v>
-      </c>
-      <c r="J20" t="n">
-        <v>9</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-12.04296</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-77.11915</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -1409,20 +1587,30 @@
           <t>SAN JUAN EL BAUTISTA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-11.94282</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-77.13539</v>
-      </c>
-      <c r="I21" t="n">
-        <v>674</v>
-      </c>
-      <c r="J21" t="n">
-        <v>41</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-11.94282</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-77.13539</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -1456,20 +1644,30 @@
           <t>INTELLECTUM SANTA ISABEL</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-12.051671</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-77.11158500000001</v>
-      </c>
-      <c r="I22" t="n">
-        <v>353</v>
-      </c>
-      <c r="J22" t="n">
-        <v>25</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-12.051671</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-77.111585</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>353</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
     <row r="23">
@@ -1503,20 +1701,30 @@
           <t>PAEBA PILOTO REGIONAL DE EXCELENCIA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-11.93978</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-77.13185</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-11.93978</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-77.13185</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>
